--- a/artfynd/A 4089-2023 artfynd.xlsx
+++ b/artfynd/A 4089-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134111952</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>134112897</v>
       </c>
       <c r="B4" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4089-2023 artfynd.xlsx
+++ b/artfynd/A 4089-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134111952</v>
+        <v>134112897</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>92406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560349</v>
+        <v>560316</v>
       </c>
       <c r="R2" t="n">
-        <v>6463709</v>
+        <v>6463690</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp men det är anmärkningsvärt med att hitta indikatorn för urskogsartad skog i Götaland och vi har inte många fynd av denna vedsvamp i Götaland. Tyvärr har markägaren tillsammans och säkert genom uppmuntran av hans ombud från Södra Skogsägarna huggit redan det mesta av denna skyddsvärda kontinuitetsskog tidigare och bara en liten spilla är kvar till vidare.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134112385</v>
+        <v>134111901</v>
       </c>
       <c r="B3" t="n">
-        <v>58134</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,31 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560335</v>
+        <v>560345</v>
       </c>
       <c r="R3" t="n">
-        <v>6463700</v>
+        <v>6463729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,17 +857,13 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Området utgörs en del av reviret som överlag sträcker sig västerut och mot nordväst från registrerad plats med observation av arten.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134112897</v>
+        <v>134111952</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560316</v>
+        <v>560349</v>
       </c>
       <c r="R4" t="n">
-        <v>6463690</v>
+        <v>6463709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,11 +958,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp men det är anmärkningsvärt med att hitta indikatorn för urskogsartad skog i Götaland och vi har inte många fynd av denna vedsvamp i Götaland. Tyvärr har markägaren tillsammans och säkert genom uppmuntran av hans ombud från Södra Skogsägarna huggit redan det mesta av denna skyddsvärda kontinuitetsskog tidigare och bara en liten spilla är kvar till vidare.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,6 +980,322 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134111988</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75468</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>560333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6463720</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134111918</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>560345</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6463729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134112385</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>560335</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6463700</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Området utgörs en del av reviret som överlag sträcker sig västerut och mot nordväst från registrerad plats med observation av arten.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4089-2023 artfynd.xlsx
+++ b/artfynd/A 4089-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134112897</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111901</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111952</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111988</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111918</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,8 +1326,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134112385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>